--- a/r5-core-76-add-healthcare-service/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r5-core-76-add-healthcare-service/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T20:51:56+00:00</t>
+    <t>2026-08-11T21:17:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-core-76-add-healthcare-service/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r5-core-76-add-healthcare-service/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T21:17:19+00:00</t>
+    <t>2026-08-11T21:36:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
